--- a/data/output/stats-fray-spring_2026.xlsx
+++ b/data/output/stats-fray-spring_2026.xlsx
@@ -4470,12 +4470,12 @@
           <t>Team OPS</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Through Date</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Workbook Season</t>
         </is>

--- a/data/output/stats-fray-spring_2026.xlsx
+++ b/data/output/stats-fray-spring_2026.xlsx
@@ -12,28 +12,28 @@
     <sheet name="Player Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Cyclo Total" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Cyclo Spring 2026 Total" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cyclo Spring 2026 Game 1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cyclo Spring 2026 Game 2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cyclo Spring 2026 Game 3" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Cyclo Spring 2026 Game 4" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Cyclo Spring 2026 Game 5" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Cyclo Spring 2026 Game 6" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Cyclo Spring 2026 Game 7" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Cyclo Spring 2026 Game 8" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Cyclo Spring 2026 Game 8" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cyclo Spring 2026 Game 7" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cyclo Spring 2026 Game 6" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Cyclo Spring 2026 Game 5" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Cyclo Spring 2026 Game 4" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Cyclo Spring 2026 Game 3" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Cyclo Spring 2026 Game 2" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Cyclo Spring 2026 Game 1" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'League Summary'!$A$1:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Player Summary'!$A$1:$Q$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cyclo Total'!$A$1:$Q$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cyclo Spring 2026 Total'!$A$1:$Q$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cyclo Spring 2026 Game 1'!$A$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cyclo Spring 2026 Game 2'!$A$1:$Q$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cyclo Spring 2026 Game 3'!$A$1:$Q$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cyclo Spring 2026 Game 4'!$A$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cyclo Spring 2026 Game 5'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Cyclo Spring 2026 Game 6'!$A$1:$Q$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Cyclo Spring 2026 Game 7'!$A$1:$Q$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Cyclo Spring 2026 Game 8'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cyclo Spring 2026 Game 8'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cyclo Spring 2026 Game 7'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cyclo Spring 2026 Game 6'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cyclo Spring 2026 Game 5'!$A$1:$Q$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cyclo Spring 2026 Game 4'!$A$1:$Q$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Cyclo Spring 2026 Game 3'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Cyclo Spring 2026 Game 2'!$A$1:$Q$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Cyclo Spring 2026 Game 1'!$A$1:$Q$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -905,13 +905,13 @@
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -940,12 +940,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -986,61 +986,61 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>3.500</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -1049,61 +1049,61 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>2.083</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>3</v>
@@ -1129,19 +1129,19 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1151,10 +1151,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1175,49 +1175,49 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1238,61 +1238,61 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1301,58 +1301,58 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.800</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>2.250</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>3.250</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1364,61 +1364,61 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1427,223 +1427,160 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.400</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.833</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.667</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.750</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C12" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1.250</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1.750</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TEAM TOTALS</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0.795</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0.795</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1.250</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2.045</t>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1.167</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1.834</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q12"/>
+  <autoFilter ref="A1:Q11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1655,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1771,19 +1708,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1798,61 +1735,61 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1864,10 +1801,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -1881,19 +1818,19 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.667</t>
+          <t>3.500</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1903,7 +1840,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1915,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1930,43 +1867,43 @@
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>4.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1.666</t>
+          <t>5.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1978,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1990,52 +1927,52 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>2.500</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>3.500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2053,46 +1990,46 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2104,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2113,46 +2050,46 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -2186,29 +2123,29 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2242,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -2271,20 +2208,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -2293,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2305,10 +2242,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2322,19 +2259,19 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2344,10 +2281,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -2371,157 +2308,220 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.333</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.333</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Stephen</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0.333</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0.666</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E14" s="2" t="n">
+      <c r="B15" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0.722</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1.222</t>
+      <c r="M15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>1.429</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>2.000</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q12"/>
+  <autoFilter ref="A1:Q13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2652,56 +2652,56 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.333</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>3.333</t>
         </is>
       </c>
     </row>
@@ -2712,19 +2712,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2739,32 +2739,32 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -2778,25 +2778,25 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2805,10 +2805,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.333</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>3.333</t>
         </is>
       </c>
     </row>
@@ -2844,19 +2844,19 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2868,49 +2868,49 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
         <v>2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.334</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Briana</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2931,46 +2931,46 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -2982,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2994,49 +2994,49 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.667</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.334</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -3045,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3057,49 +3057,49 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -3120,29 +3120,29 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>1.000</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -3153,16 +3153,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -3174,16 +3174,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -3195,34 +3195,34 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Kunal</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3231,13 +3231,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -3253,42 +3253,42 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -3306,32 +3306,32 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
@@ -3342,22 +3342,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -3372,29 +3372,29 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
@@ -3405,59 +3405,59 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>0.694</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>0.694</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>1.222</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>1.408</t>
+          <t>1.916</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3599,7 +3599,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -3608,7 +3608,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -3637,12 +3637,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.666</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
@@ -3653,16 +3653,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -3683,19 +3683,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3705,14 +3705,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -3722,10 +3722,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -3746,46 +3746,46 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -3794,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3809,36 +3809,36 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -3848,10 +3848,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3875,26 +3875,26 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3935,10 +3935,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -3952,12 +3952,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>4.000</t>
         </is>
       </c>
     </row>
@@ -3971,13 +3971,13 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -3989,7 +3989,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3998,14 +3998,14 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -4015,19 +4015,19 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.417</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -4037,13 +4037,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4061,52 +4061,52 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.333</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -4115,45 +4115,45 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.750</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -4163,10 +4163,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -4187,223 +4187,97 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>0.500</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.000</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>1.500</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2.500</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B13" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0.469</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0.469</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>0.906</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1.375</t>
+      <c r="C13" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0.676</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.676</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1.029</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1.705</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q13"/>
+  <autoFilter ref="A1:Q11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8624,7 +8498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8749,7 +8623,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -8758,7 +8632,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -8770,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -8787,12 +8661,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>1.666</t>
         </is>
       </c>
     </row>
@@ -8803,16 +8677,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -8833,19 +8707,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -8855,14 +8729,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -8872,10 +8746,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -8896,46 +8770,46 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -8944,7 +8818,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -8959,36 +8833,36 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1.250</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -8998,10 +8872,10 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -9025,26 +8899,26 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
@@ -9055,16 +8929,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -9073,7 +8947,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9085,10 +8959,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -9102,12 +8976,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -9121,13 +8995,13 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -9139,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -9148,36 +9022,36 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>0.667</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>0.750</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0.750</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.417</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -9187,13 +9061,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -9211,52 +9085,52 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.333</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -9265,45 +9139,45 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -9313,10 +9187,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -9325,7 +9199,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -9337,97 +9211,223 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>0.500</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stephen</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1.500</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B15" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0.676</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0.676</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1.029</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1.705</t>
+      <c r="C15" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0.469</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.469</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>0.906</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>1.375</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q11"/>
+  <autoFilter ref="A1:Q13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9558,56 +9558,56 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2.333</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>3.333</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -9618,19 +9618,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -9645,32 +9645,32 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1.500</t>
         </is>
       </c>
     </row>
@@ -9684,25 +9684,25 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -9728,12 +9728,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.333</t>
+          <t>3.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3.333</t>
+          <t>4.000</t>
         </is>
       </c>
     </row>
@@ -9750,19 +9750,19 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9774,49 +9774,49 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.667</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.334</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Briana</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -9837,46 +9837,46 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -9888,7 +9888,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9900,49 +9900,49 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.334</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -9951,7 +9951,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -9963,49 +9963,49 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.334</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -10026,29 +10026,29 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -10059,16 +10059,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -10080,16 +10080,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -10111,24 +10111,24 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10137,13 +10137,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -10159,42 +10159,42 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.250</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -10212,32 +10212,32 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
@@ -10248,22 +10248,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10278,29 +10278,29 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
@@ -10311,59 +10311,59 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>0.519</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>0.519</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>0.889</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>1.916</t>
+          <t>1.408</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10496,19 +10496,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10523,22 +10523,22 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -10548,36 +10548,36 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -10589,10 +10589,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -10606,19 +10606,19 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.667</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>2.667</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -10628,7 +10628,7 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -10640,7 +10640,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -10655,43 +10655,43 @@
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>4.000</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>5.000</t>
+          <t>1.666</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -10703,7 +10703,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10715,52 +10715,52 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>0.666</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -10778,46 +10778,46 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.667</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -10838,46 +10838,46 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -10911,29 +10911,29 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>0.500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -10967,7 +10967,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -10996,20 +10996,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -11030,10 +11030,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -11047,19 +11047,19 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -11069,10 +11069,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -11096,40 +11096,40 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>2.333</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -11163,153 +11163,90 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.333</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.666</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TEAM TOTALS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>0.500</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0.500</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Stephen</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0.500</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TEAM TOTALS</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0.571</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0.571</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>1.429</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2.000</t>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0.722</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1.222</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q13"/>
+  <autoFilter ref="A1:Q12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11321,7 +11258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11449,13 +11386,13 @@
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -11484,12 +11421,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
@@ -11500,25 +11437,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -11530,61 +11467,61 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2.500</t>
+          <t>1.333</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3.500</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -11593,61 +11530,61 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2.083</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cory</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -11656,7 +11593,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>3</v>
@@ -11673,19 +11610,19 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.000</t>
+          <t>1.500</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3.000</t>
+          <t>2.500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Cory</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -11695,10 +11632,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -11719,49 +11656,49 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.750</t>
+          <t>0.500</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.500</t>
+          <t>1.000</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -11782,61 +11719,61 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kap</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -11845,58 +11782,58 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.800</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2.250</t>
+          <t>0.667</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3.250</t>
+          <t>1.467</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kyla</t>
+          <t>Kap</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -11908,61 +11845,61 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>2.000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>3.000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kyla</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -11971,160 +11908,223 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.500</t>
+          <t>0.600</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>1.400</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>2.000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.750</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Stephen</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1.667</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1.250</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1.750</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TEAM TOTALS</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="D13" s="2" t="n">
+      <c r="B14" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1.167</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1.834</t>
+      <c r="M14" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0.795</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.795</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1.250</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2.045</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q11"/>
+  <autoFilter ref="A1:Q12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>